--- a/timesheets/scott-timesheet.xlsx
+++ b/timesheets/scott-timesheet.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Code/Apps/RagFactory/Working Documents/timesheets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10A6A89C-5C8F-1F4F-BAF4-96D570E5FD44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88B8E2CB-BECE-B14C-A87E-EAC4D883DA7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="102400" windowHeight="28200" xr2:uid="{C46E0534-C623-F74E-979A-96D92E3EAC56}"/>
   </bookViews>
@@ -467,7 +467,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9090A6B0-3C3B-5444-8457-BF107066D44E}">
-  <dimension ref="A1:I93"/>
+  <dimension ref="A1:I95"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="26.1640625" bestFit="1" customWidth="1"/>
@@ -560,7 +560,7 @@
         <v>2</v>
       </c>
       <c r="D5" s="5">
-        <f t="shared" ref="D5:D25" si="0">SUM(B5*$B$1)+(C5*$D$1)</f>
+        <f t="shared" ref="D5:D27" si="0">SUM(B5*$B$1)+(C5*$D$1)</f>
         <v>700</v>
       </c>
       <c r="E5" s="1" t="s">
@@ -981,70 +981,100 @@
       <c r="I25" s="1"/>
     </row>
     <row r="26" spans="1:9" ht="21" x14ac:dyDescent="0.25">
-      <c r="A26" s="6"/>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="5"/>
+      <c r="A26" s="6">
+        <v>46144</v>
+      </c>
+      <c r="B26" s="1">
+        <v>2.34</v>
+      </c>
+      <c r="C26" s="1">
+        <v>0</v>
+      </c>
+      <c r="D26" s="5">
+        <f t="shared" si="0"/>
+        <v>374.4</v>
+      </c>
       <c r="E26" s="1"/>
       <c r="G26" s="1"/>
       <c r="H26" s="5"/>
       <c r="I26" s="1"/>
     </row>
     <row r="27" spans="1:9" ht="21" x14ac:dyDescent="0.25">
-      <c r="A27" s="1"/>
-      <c r="B27" s="1"/>
-      <c r="C27" s="4" t="s">
-        <v>4</v>
+      <c r="A27" s="6">
+        <v>46151</v>
+      </c>
+      <c r="B27" s="1">
+        <v>1.6</v>
+      </c>
+      <c r="C27" s="1">
+        <v>0</v>
       </c>
       <c r="D27" s="5">
-        <f>SUM(D4:D25)</f>
-        <v>9557.3999999999978</v>
+        <f t="shared" si="0"/>
+        <v>256</v>
       </c>
       <c r="E27" s="1"/>
-      <c r="G27" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="H27" s="5">
-        <f>SUM(H4:H18)</f>
-        <v>10000</v>
-      </c>
+      <c r="G27" s="1"/>
+      <c r="H27" s="5"/>
       <c r="I27" s="1"/>
     </row>
     <row r="28" spans="1:9" ht="21" x14ac:dyDescent="0.25">
-      <c r="A28" s="1"/>
+      <c r="A28" s="6"/>
       <c r="B28" s="1"/>
-      <c r="C28" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D28" s="5">
-        <f>SUM(H27-D27)</f>
-        <v>442.60000000000218</v>
-      </c>
+      <c r="C28" s="1"/>
+      <c r="D28" s="5"/>
       <c r="E28" s="1"/>
       <c r="G28" s="1"/>
       <c r="H28" s="5"/>
       <c r="I28" s="1"/>
     </row>
     <row r="29" spans="1:9" ht="21" x14ac:dyDescent="0.25">
-      <c r="C29" s="8" t="s">
+      <c r="A29" s="1"/>
+      <c r="B29" s="1"/>
+      <c r="C29" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D29" s="5">
+        <f>SUM(D4:D27)</f>
+        <v>10187.799999999997</v>
+      </c>
+      <c r="E29" s="1"/>
+      <c r="G29" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H29" s="5">
+        <f>SUM(H4:H18)</f>
+        <v>10000</v>
+      </c>
+      <c r="I29" s="1"/>
+    </row>
+    <row r="30" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A30" s="1"/>
+      <c r="B30" s="1"/>
+      <c r="C30" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D30" s="5">
+        <f>SUM(H29-D29)</f>
+        <v>-187.79999999999745</v>
+      </c>
+      <c r="E30" s="1"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="5"/>
+      <c r="I30" s="1"/>
+    </row>
+    <row r="31" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="C31" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D29" s="5">
+      <c r="D31" s="5">
         <f>SUM(B4:B25)</f>
         <v>57.390000000000008</v>
       </c>
-      <c r="E29" s="1"/>
-    </row>
-    <row r="30" spans="1:9" ht="21" x14ac:dyDescent="0.25">
-      <c r="C30" s="8"/>
-      <c r="D30" s="3"/>
-      <c r="E30" s="1"/>
-    </row>
-    <row r="31" spans="1:9" ht="21" x14ac:dyDescent="0.25">
-      <c r="D31" s="3"/>
       <c r="E31" s="1"/>
     </row>
     <row r="32" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="C32" s="8"/>
       <c r="D32" s="3"/>
       <c r="E32" s="1"/>
     </row>
@@ -1120,11 +1150,13 @@
       <c r="D50" s="3"/>
       <c r="E50" s="1"/>
     </row>
-    <row r="51" spans="4:5" x14ac:dyDescent="0.2">
+    <row r="51" spans="4:5" ht="21" x14ac:dyDescent="0.25">
       <c r="D51" s="3"/>
-    </row>
-    <row r="52" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="E51" s="1"/>
+    </row>
+    <row r="52" spans="4:5" ht="21" x14ac:dyDescent="0.25">
       <c r="D52" s="3"/>
+      <c r="E52" s="1"/>
     </row>
     <row r="53" spans="4:5" x14ac:dyDescent="0.2">
       <c r="D53" s="3"/>
@@ -1248,6 +1280,12 @@
     </row>
     <row r="93" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D93" s="3"/>
+    </row>
+    <row r="94" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D94" s="3"/>
+    </row>
+    <row r="95" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D95" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
